--- a/데이터 베이스/2. 12개 입력값 머신러닝 전단파괴만.xlsx
+++ b/데이터 베이스/2. 12개 입력값 머신러닝 전단파괴만.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yjy98\Documents\Punching-shear\데이터 베이스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B482BDC-0343-4C1A-8258-17A182C3DDA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D40C370-3D6C-4E78-9931-75DFC166416B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5677" yWindow="570" windowWidth="16200" windowHeight="9983" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NEES_Database__ACI_445_Punching" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3108,6 +3111,9 @@
       <c r="J47">
         <v>9.2230239999999998E-3</v>
       </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
       <c r="L47">
         <v>15.118332744613211</v>
       </c>
@@ -9397,6 +9403,9 @@
       <c r="J190">
         <v>0</v>
       </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
       <c r="L190">
         <v>22.881720430107528</v>
       </c>
@@ -9438,6 +9447,9 @@
       <c r="J191">
         <v>0</v>
       </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
       <c r="L191">
         <v>20.324737344794652</v>
       </c>
@@ -9479,6 +9491,9 @@
       <c r="J192">
         <v>0</v>
       </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
       <c r="L192">
         <v>15.377777777777778</v>
       </c>
@@ -9520,6 +9535,9 @@
       <c r="J193">
         <v>0</v>
       </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
       <c r="L193">
         <v>14.50733752620545</v>
       </c>
@@ -9561,6 +9579,9 @@
       <c r="J194">
         <v>0</v>
       </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
       <c r="L194">
         <v>15.638418079096045</v>
       </c>
@@ -9602,6 +9623,9 @@
       <c r="J195">
         <v>0</v>
       </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
       <c r="L195">
         <v>14.50733752620545</v>
       </c>
@@ -9643,6 +9667,9 @@
       <c r="J196">
         <v>0</v>
       </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
       <c r="L196">
         <v>15.638418079096045</v>
       </c>
@@ -9684,6 +9711,9 @@
       <c r="J197">
         <v>0</v>
       </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
       <c r="L197">
         <v>16.898656898656899</v>
       </c>
@@ -9725,6 +9755,9 @@
       <c r="J198">
         <v>0</v>
       </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
       <c r="L198">
         <v>26.970849176172369</v>
       </c>
@@ -9766,6 +9799,9 @@
       <c r="J199">
         <v>1.0471980000000001E-3</v>
       </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
       <c r="L199">
         <v>29.852104664391351</v>
       </c>
@@ -9807,6 +9843,9 @@
       <c r="J200">
         <v>0</v>
       </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
       <c r="L200">
         <v>17.541191381495562</v>
       </c>
@@ -9848,6 +9887,9 @@
       <c r="J201">
         <v>0</v>
       </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
       <c r="L201">
         <v>16.359338061465721</v>
       </c>
@@ -9889,6 +9931,9 @@
       <c r="J202">
         <v>0</v>
       </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
       <c r="L202">
         <v>16.359338061465721</v>
       </c>
@@ -13978,6 +14023,9 @@
       <c r="J295">
         <v>9.7999999999999997E-3</v>
       </c>
+      <c r="K295">
+        <v>0</v>
+      </c>
       <c r="L295">
         <v>11.853388296399972</v>
       </c>
@@ -14283,6 +14331,9 @@
       <c r="J302">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
       <c r="L302">
         <v>11.564444105186825</v>
       </c>
@@ -14324,6 +14375,9 @@
       <c r="J303">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K303">
+        <v>0</v>
+      </c>
       <c r="L303">
         <v>13.891224150374564</v>
       </c>
@@ -14365,6 +14419,9 @@
       <c r="J304">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K304">
+        <v>0</v>
+      </c>
       <c r="L304">
         <v>15.01299498979332</v>
       </c>
@@ -14406,6 +14463,9 @@
       <c r="J305">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K305">
+        <v>0</v>
+      </c>
       <c r="L305">
         <v>14.121598412274341</v>
       </c>
@@ -14447,6 +14507,9 @@
       <c r="J306">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
       <c r="L306">
         <v>14.719581406930908</v>
       </c>
@@ -14488,6 +14551,9 @@
       <c r="J307">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
       <c r="L307">
         <v>15.163787538887727</v>
       </c>
@@ -14529,6 +14595,9 @@
       <c r="J308">
         <v>2.6179938999999999E-2</v>
       </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
       <c r="L308">
         <v>14.405865089752956</v>
       </c>
@@ -14570,6 +14639,9 @@
       <c r="J309">
         <v>2.6179938999999999E-2</v>
       </c>
+      <c r="K309">
+        <v>0</v>
+      </c>
       <c r="L309">
         <v>19.982705964691871</v>
       </c>
@@ -14611,6 +14683,9 @@
       <c r="J310">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
       <c r="L310">
         <v>16.044247743240465</v>
       </c>
@@ -14652,6 +14727,9 @@
       <c r="J311">
         <v>2.6179938999999999E-2</v>
       </c>
+      <c r="K311">
+        <v>0</v>
+      </c>
       <c r="L311">
         <v>15.507011663616854</v>
       </c>
@@ -14693,6 +14771,9 @@
       <c r="J312">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K312">
+        <v>0</v>
+      </c>
       <c r="L312">
         <v>20.390674224774695</v>
       </c>
@@ -14734,6 +14815,9 @@
       <c r="J313">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K313">
+        <v>0</v>
+      </c>
       <c r="L313">
         <v>18.376894071035835</v>
       </c>
@@ -14775,6 +14859,9 @@
       <c r="J314">
         <v>1.3089969E-2</v>
       </c>
+      <c r="K314">
+        <v>0</v>
+      </c>
       <c r="L314">
         <v>16.93363462919508</v>
       </c>
@@ -14816,6 +14903,9 @@
       <c r="J315">
         <v>2.6179938999999999E-2</v>
       </c>
+      <c r="K315">
+        <v>0</v>
+      </c>
       <c r="L315">
         <v>20.219300266693079</v>
       </c>
@@ -14856,6 +14946,9 @@
       </c>
       <c r="J316">
         <v>2.6179938999999999E-2</v>
+      </c>
+      <c r="K316">
+        <v>0</v>
       </c>
       <c r="L316">
         <v>18.544995835938931</v>

--- a/데이터 베이스/2. 12개 입력값 머신러닝 전단파괴만.xlsx
+++ b/데이터 베이스/2. 12개 입력값 머신러닝 전단파괴만.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yjy98\Documents\Punching-shear\데이터 베이스\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSC-3\Desktop\code\Punching-shear\데이터 베이스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D40C370-3D6C-4E78-9931-75DFC166416B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366A4602-69F3-43C4-9BD7-444F817ADF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28455" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NEES_Database__ACI_445_Punching" sheetId="1" r:id="rId1"/>
@@ -691,13 +691,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -757,9 +758,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -797,7 +798,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -903,7 +904,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1045,7 +1046,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1053,10 +1054,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N473"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:O474"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1100,7 +1101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1143,8 +1144,9 @@
       <c r="N2">
         <v>600</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1187,8 +1189,9 @@
       <c r="N3">
         <v>311</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1231,8 +1234,9 @@
       <c r="N4">
         <v>401</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1275,8 +1279,9 @@
       <c r="N5">
         <v>188</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1319,8 +1324,9 @@
       <c r="N6">
         <v>202</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1363,8 +1369,9 @@
       <c r="N7">
         <v>331</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1407,8 +1414,9 @@
       <c r="N8">
         <v>371</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1451,8 +1459,9 @@
       <c r="N9">
         <v>405</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1495,8 +1504,9 @@
       <c r="N10">
         <v>489</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1539,8 +1549,9 @@
       <c r="N11">
         <v>1024</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -1583,8 +1594,9 @@
       <c r="N12">
         <v>2153</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>14</v>
       </c>
@@ -1627,8 +1639,9 @@
       <c r="N13">
         <v>550</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>15</v>
       </c>
@@ -1671,8 +1684,9 @@
       <c r="N14">
         <v>236</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16</v>
       </c>
@@ -1715,8 +1729,9 @@
       <c r="N15">
         <v>243</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>19</v>
       </c>
@@ -1759,8 +1774,9 @@
       <c r="N16">
         <v>540</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>20</v>
       </c>
@@ -1803,8 +1819,9 @@
       <c r="N17">
         <v>483</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>21</v>
       </c>
@@ -1847,8 +1864,9 @@
       <c r="N18">
         <v>825</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>22</v>
       </c>
@@ -1891,8 +1909,9 @@
       <c r="N19">
         <v>1046</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>23</v>
       </c>
@@ -1935,8 +1954,9 @@
       <c r="N20">
         <v>789</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>24</v>
       </c>
@@ -1979,8 +1999,9 @@
       <c r="N21">
         <v>668</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25</v>
       </c>
@@ -2023,8 +2044,9 @@
       <c r="N22">
         <v>1356</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26</v>
       </c>
@@ -2067,8 +2089,9 @@
       <c r="N23">
         <v>170</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>27</v>
       </c>
@@ -2111,8 +2134,9 @@
       <c r="N24">
         <v>229</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>28</v>
       </c>
@@ -2155,8 +2179,9 @@
       <c r="N25">
         <v>271</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>29</v>
       </c>
@@ -2199,8 +2224,9 @@
       <c r="N26">
         <v>237</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>30</v>
       </c>
@@ -2243,8 +2269,9 @@
       <c r="N27">
         <v>317</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>31</v>
       </c>
@@ -2287,8 +2314,9 @@
       <c r="N28">
         <v>240</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>32</v>
       </c>
@@ -2331,8 +2359,9 @@
       <c r="N29">
         <v>322</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>33</v>
       </c>
@@ -2375,8 +2404,9 @@
       <c r="N30">
         <v>318</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>34</v>
       </c>
@@ -2419,8 +2449,9 @@
       <c r="N31">
         <v>246</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>35</v>
       </c>
@@ -2463,8 +2494,9 @@
       <c r="N32">
         <v>361</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>36</v>
       </c>
@@ -2507,8 +2539,9 @@
       <c r="N33">
         <v>331</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>37</v>
       </c>
@@ -2551,8 +2584,9 @@
       <c r="N34">
         <v>241</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>38</v>
       </c>
@@ -2595,8 +2629,9 @@
       <c r="N35">
         <v>400</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>39</v>
       </c>
@@ -2639,8 +2674,9 @@
       <c r="N36">
         <v>358</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>40</v>
       </c>
@@ -2683,8 +2719,9 @@
       <c r="N37">
         <v>251</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O37" s="2"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>41</v>
       </c>
@@ -2727,8 +2764,9 @@
       <c r="N38">
         <v>395</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>42</v>
       </c>
@@ -2771,8 +2809,9 @@
       <c r="N39">
         <v>404</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O39" s="2"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>43</v>
       </c>
@@ -2815,8 +2854,9 @@
       <c r="N40">
         <v>287</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O40" s="2"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>44</v>
       </c>
@@ -2859,8 +2899,9 @@
       <c r="N41">
         <v>426</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O41" s="2"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>45</v>
       </c>
@@ -2903,8 +2944,9 @@
       <c r="N42">
         <v>446</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O42" s="2"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>46</v>
       </c>
@@ -2947,8 +2989,9 @@
       <c r="N43">
         <v>365</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O43" s="2"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>47</v>
       </c>
@@ -2991,8 +3034,9 @@
       <c r="N44">
         <v>199</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O44" s="2"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>48</v>
       </c>
@@ -3035,8 +3079,9 @@
       <c r="N45">
         <v>249</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O45" s="2"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>49</v>
       </c>
@@ -3079,8 +3124,9 @@
       <c r="N46">
         <v>203</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O46" s="2"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>50</v>
       </c>
@@ -3123,8 +3169,9 @@
       <c r="N47">
         <v>541</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O47" s="2"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>51</v>
       </c>
@@ -3167,8 +3214,9 @@
       <c r="N48">
         <v>330</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O48" s="2"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>52</v>
       </c>
@@ -3211,8 +3259,9 @@
       <c r="N49">
         <v>583</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>53</v>
       </c>
@@ -3255,8 +3304,9 @@
       <c r="N50">
         <v>904</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O50" s="2"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>54</v>
       </c>
@@ -3299,8 +3349,9 @@
       <c r="N51">
         <v>1381</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O51" s="2"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>55</v>
       </c>
@@ -3343,8 +3394,9 @@
       <c r="N52">
         <v>2224</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O52" s="2"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>56</v>
       </c>
@@ -3387,8 +3439,9 @@
       <c r="N53">
         <v>2681</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O53" s="2"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>57</v>
       </c>
@@ -3431,8 +3484,9 @@
       <c r="N54">
         <v>240</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O54" s="2"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>58</v>
       </c>
@@ -3475,8 +3529,9 @@
       <c r="N55">
         <v>265</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O55" s="2"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>59</v>
       </c>
@@ -3519,8 +3574,9 @@
       <c r="N56">
         <v>294</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O56" s="2"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>60</v>
       </c>
@@ -3563,8 +3619,9 @@
       <c r="N57">
         <v>313</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O57" s="2"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>61</v>
       </c>
@@ -3607,8 +3664,9 @@
       <c r="N58">
         <v>181</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O58" s="2"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>62</v>
       </c>
@@ -3651,8 +3709,9 @@
       <c r="N59">
         <v>189</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O59" s="2"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>63</v>
       </c>
@@ -3695,8 +3754,9 @@
       <c r="N60">
         <v>255</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O60" s="2"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>64</v>
       </c>
@@ -3739,8 +3799,9 @@
       <c r="N61">
         <v>273</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O61" s="2"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>65</v>
       </c>
@@ -3783,8 +3844,9 @@
       <c r="N62">
         <v>347</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O62" s="2"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>66</v>
       </c>
@@ -3827,8 +3889,9 @@
       <c r="N63">
         <v>343</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>67</v>
       </c>
@@ -3871,8 +3934,9 @@
       <c r="N64">
         <v>142</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O64" s="2"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>68</v>
       </c>
@@ -3915,8 +3979,9 @@
       <c r="N65">
         <v>150</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>69</v>
       </c>
@@ -3959,8 +4024,9 @@
       <c r="N66">
         <v>207</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O66" s="2"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>70</v>
       </c>
@@ -4003,8 +4069,9 @@
       <c r="N67">
         <v>231</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O67" s="2"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>71</v>
       </c>
@@ -4047,8 +4114,9 @@
       <c r="N68">
         <v>171</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O68" s="2"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>72</v>
       </c>
@@ -4091,8 +4159,9 @@
       <c r="N69">
         <v>237</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O69" s="2"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>73</v>
       </c>
@@ -4135,8 +4204,9 @@
       <c r="N70">
         <v>217</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O70" s="2"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>74</v>
       </c>
@@ -4179,8 +4249,9 @@
       <c r="N71">
         <v>306</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O71" s="2"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>75</v>
       </c>
@@ -4223,8 +4294,9 @@
       <c r="N72">
         <v>349</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O72" s="2"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>76</v>
       </c>
@@ -4267,8 +4339,9 @@
       <c r="N73">
         <v>120</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O73" s="2"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>77</v>
       </c>
@@ -4311,8 +4384,9 @@
       <c r="N74">
         <v>170</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O74" s="2"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>78</v>
       </c>
@@ -4355,8 +4429,9 @@
       <c r="N75">
         <v>135</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O75" s="2"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>79</v>
       </c>
@@ -4399,8 +4474,9 @@
       <c r="N76">
         <v>180</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O76" s="2"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>80</v>
       </c>
@@ -4443,8 +4519,9 @@
       <c r="N77">
         <v>301</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O77" s="2"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>81</v>
       </c>
@@ -4487,8 +4564,9 @@
       <c r="N78">
         <v>317</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O78" s="2"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>82</v>
       </c>
@@ -4531,8 +4609,9 @@
       <c r="N79">
         <v>363</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O79" s="2"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>83</v>
       </c>
@@ -4575,8 +4654,9 @@
       <c r="N80">
         <v>447</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>84</v>
       </c>
@@ -4619,8 +4699,9 @@
       <c r="N81">
         <v>443</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O81" s="2"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>85</v>
       </c>
@@ -4663,8 +4744,9 @@
       <c r="N82">
         <v>485</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O82" s="2"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>86</v>
       </c>
@@ -4707,8 +4789,9 @@
       <c r="N83">
         <v>503</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O83" s="2"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>87</v>
       </c>
@@ -4751,8 +4834,9 @@
       <c r="N84">
         <v>537</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O84" s="2"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>88</v>
       </c>
@@ -4795,8 +4879,9 @@
       <c r="N85">
         <v>530</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O85" s="2"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>89</v>
       </c>
@@ -4839,8 +4924,9 @@
       <c r="N86">
         <v>686</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O86" s="2"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>90</v>
       </c>
@@ -4883,8 +4969,9 @@
       <c r="N87">
         <v>696</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O87" s="2"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>91</v>
       </c>
@@ -4927,8 +5014,9 @@
       <c r="N88">
         <v>799</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O88" s="2"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>92</v>
       </c>
@@ -4971,8 +5059,9 @@
       <c r="N89">
         <v>478</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O89" s="2"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5015,8 +5104,9 @@
       <c r="N90">
         <v>1111</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O90" s="2"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5059,8 +5149,9 @@
       <c r="N91">
         <v>1107</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O91" s="2"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5103,8 +5194,9 @@
       <c r="N92">
         <v>1079</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O92" s="2"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5147,8 +5239,9 @@
       <c r="N93">
         <v>965</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O93" s="2"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5191,8 +5284,9 @@
       <c r="N94">
         <v>1021</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O94" s="2"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>98</v>
       </c>
@@ -5235,8 +5329,9 @@
       <c r="N95">
         <v>889</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O95" s="2"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>99</v>
       </c>
@@ -5279,8 +5374,9 @@
       <c r="N96">
         <v>1041</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O96" s="2"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>100</v>
       </c>
@@ -5323,8 +5419,9 @@
       <c r="N97">
         <v>960</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O97" s="2"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>101</v>
       </c>
@@ -5367,8 +5464,9 @@
       <c r="N98">
         <v>565</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O98" s="2"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>103</v>
       </c>
@@ -5411,8 +5509,9 @@
       <c r="N99">
         <v>212</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O99" s="2"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>104</v>
       </c>
@@ -5455,8 +5554,9 @@
       <c r="N100">
         <v>169</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O100" s="2"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>107</v>
       </c>
@@ -5499,8 +5599,9 @@
       <c r="N101">
         <v>319</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O101" s="2"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>108</v>
       </c>
@@ -5543,8 +5644,9 @@
       <c r="N102">
         <v>297</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O102" s="2"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>109</v>
       </c>
@@ -5587,8 +5689,9 @@
       <c r="N103">
         <v>341</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O103" s="2"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>110</v>
       </c>
@@ -5631,8 +5734,9 @@
       <c r="N104">
         <v>362</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O104" s="2"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>111</v>
       </c>
@@ -5675,8 +5779,9 @@
       <c r="N105">
         <v>286</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O105" s="2"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>112</v>
       </c>
@@ -5719,8 +5824,9 @@
       <c r="N106">
         <v>405</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O106" s="2"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>113</v>
       </c>
@@ -5763,8 +5869,9 @@
       <c r="N107">
         <v>341</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O107" s="2"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>114</v>
       </c>
@@ -5807,8 +5914,9 @@
       <c r="N108">
         <v>244</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O108" s="2"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>115</v>
       </c>
@@ -5851,8 +5959,9 @@
       <c r="N109">
         <v>294</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O109" s="2"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>116</v>
       </c>
@@ -5895,8 +6004,9 @@
       <c r="N110">
         <v>227</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O110" s="2"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>117</v>
       </c>
@@ -5939,8 +6049,9 @@
       <c r="N111">
         <v>65</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O111" s="2"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>118</v>
       </c>
@@ -5983,8 +6094,9 @@
       <c r="N112">
         <v>61</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O112" s="2"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>119</v>
       </c>
@@ -6027,8 +6139,9 @@
       <c r="N113">
         <v>60</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O113" s="2"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>128</v>
       </c>
@@ -6071,8 +6184,9 @@
       <c r="N114">
         <v>260</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O114" s="2"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>129</v>
       </c>
@@ -6115,8 +6229,9 @@
       <c r="N115">
         <v>360</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O115" s="2"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>130</v>
       </c>
@@ -6159,8 +6274,9 @@
       <c r="N116">
         <v>252</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O116" s="2"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>131</v>
       </c>
@@ -6203,8 +6319,9 @@
       <c r="N117">
         <v>220</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O117" s="2"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>132</v>
       </c>
@@ -6247,8 +6364,9 @@
       <c r="N118">
         <v>210</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O118" s="2"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>133</v>
       </c>
@@ -6291,8 +6409,9 @@
       <c r="N119">
         <v>174</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O119" s="2"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>134</v>
       </c>
@@ -6335,8 +6454,9 @@
       <c r="N120">
         <v>137</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O120" s="2"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>135</v>
       </c>
@@ -6379,8 +6499,9 @@
       <c r="N121">
         <v>150</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O121" s="2"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>136</v>
       </c>
@@ -6423,8 +6544,9 @@
       <c r="N122">
         <v>191</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O122" s="2"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>137</v>
       </c>
@@ -6467,8 +6589,9 @@
       <c r="N123">
         <v>2050</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O123" s="2"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>138</v>
       </c>
@@ -6511,8 +6634,9 @@
       <c r="N124">
         <v>1200</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O124" s="2"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>139</v>
       </c>
@@ -6555,8 +6679,9 @@
       <c r="N125">
         <v>2250</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O125" s="2"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>140</v>
       </c>
@@ -6599,8 +6724,9 @@
       <c r="N126">
         <v>2400</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O126" s="2"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>141</v>
       </c>
@@ -6643,8 +6769,9 @@
       <c r="N127">
         <v>1100</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O127" s="2"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>142</v>
       </c>
@@ -6687,8 +6814,9 @@
       <c r="N128">
         <v>1300</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O128" s="2"/>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>143</v>
       </c>
@@ -6731,8 +6859,9 @@
       <c r="N129">
         <v>1450</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O129" s="2"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>144</v>
       </c>
@@ -6775,8 +6904,9 @@
       <c r="N130">
         <v>1250</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O130" s="2"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>145</v>
       </c>
@@ -6819,8 +6949,9 @@
       <c r="N131">
         <v>1450</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O131" s="2"/>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>146</v>
       </c>
@@ -6863,8 +6994,9 @@
       <c r="N132">
         <v>330</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O132" s="2"/>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>147</v>
       </c>
@@ -6907,8 +7039,9 @@
       <c r="N133">
         <v>2450</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O133" s="2"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>148</v>
       </c>
@@ -6951,8 +7084,9 @@
       <c r="N134">
         <v>1400</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O134" s="2"/>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>149</v>
       </c>
@@ -6995,8 +7129,9 @@
       <c r="N135">
         <v>1550</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O135" s="2"/>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>150</v>
       </c>
@@ -7039,8 +7174,9 @@
       <c r="N136">
         <v>257</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O136" s="2"/>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>151</v>
       </c>
@@ -7083,8 +7219,9 @@
       <c r="N137">
         <v>264</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O137" s="2"/>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>152</v>
       </c>
@@ -7127,8 +7264,9 @@
       <c r="N138">
         <v>258</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O138" s="2"/>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>153</v>
       </c>
@@ -7171,8 +7309,9 @@
       <c r="N139">
         <v>258</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O139" s="2"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>154</v>
       </c>
@@ -7215,8 +7354,9 @@
       <c r="N140">
         <v>319</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O140" s="2"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>155</v>
       </c>
@@ -7259,8 +7399,9 @@
       <c r="N141">
         <v>304</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O141" s="2"/>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>156</v>
       </c>
@@ -7303,8 +7444,9 @@
       <c r="N142">
         <v>282</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O142" s="2"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>157</v>
       </c>
@@ -7347,8 +7489,9 @@
       <c r="N143">
         <v>343</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O143" s="2"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>158</v>
       </c>
@@ -7391,8 +7534,9 @@
       <c r="N144">
         <v>178</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O144" s="2"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>159</v>
       </c>
@@ -7435,8 +7579,9 @@
       <c r="N145">
         <v>249</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O145" s="2"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>160</v>
       </c>
@@ -7479,8 +7624,9 @@
       <c r="N146">
         <v>356</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O146" s="2"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>161</v>
       </c>
@@ -7523,8 +7669,9 @@
       <c r="N147">
         <v>418</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O147" s="2"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>162</v>
       </c>
@@ -7567,8 +7714,9 @@
       <c r="N148">
         <v>365</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O148" s="2"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>163</v>
       </c>
@@ -7611,8 +7759,9 @@
       <c r="N149">
         <v>489</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O149" s="2"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>164</v>
       </c>
@@ -7655,8 +7804,9 @@
       <c r="N150">
         <v>356</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O150" s="2"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>165</v>
       </c>
@@ -7699,8 +7849,9 @@
       <c r="N151">
         <v>436</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O151" s="2"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>166</v>
       </c>
@@ -7743,8 +7894,9 @@
       <c r="N152">
         <v>543</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O152" s="2"/>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>167</v>
       </c>
@@ -7787,8 +7939,9 @@
       <c r="N153">
         <v>645</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O153" s="2"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>168</v>
       </c>
@@ -7831,8 +7984,9 @@
       <c r="N154">
         <v>196</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O154" s="2"/>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>169</v>
       </c>
@@ -7875,8 +8029,9 @@
       <c r="N155">
         <v>258</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O155" s="2"/>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>170</v>
       </c>
@@ -7919,8 +8074,9 @@
       <c r="N156">
         <v>267</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O156" s="2"/>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>171</v>
       </c>
@@ -7963,8 +8119,9 @@
       <c r="N157">
         <v>498</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O157" s="2"/>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>172</v>
       </c>
@@ -8007,8 +8164,9 @@
       <c r="N158">
         <v>560</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O158" s="2"/>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>173</v>
       </c>
@@ -8051,8 +8209,9 @@
       <c r="N159">
         <v>320</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O159" s="2"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>174</v>
       </c>
@@ -8095,8 +8254,9 @@
       <c r="N160">
         <v>396</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O160" s="2"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>175</v>
       </c>
@@ -8139,8 +8299,9 @@
       <c r="N161">
         <v>78</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O161" s="2"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>176</v>
       </c>
@@ -8183,8 +8344,9 @@
       <c r="N162">
         <v>36</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O162" s="2"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>177</v>
       </c>
@@ -8227,8 +8389,9 @@
       <c r="N163">
         <v>24</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O163" s="2"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>178</v>
       </c>
@@ -8271,8 +8434,9 @@
       <c r="N164">
         <v>35</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O164" s="2"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>179</v>
       </c>
@@ -8315,8 +8479,9 @@
       <c r="N165">
         <v>33</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O165" s="2"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>180</v>
       </c>
@@ -8359,8 +8524,9 @@
       <c r="N166">
         <v>49</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O166" s="2"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>181</v>
       </c>
@@ -8403,8 +8569,9 @@
       <c r="N167">
         <v>34</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O167" s="2"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>182</v>
       </c>
@@ -8447,8 +8614,9 @@
       <c r="N168">
         <v>129</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O168" s="2"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>183</v>
       </c>
@@ -8491,8 +8659,9 @@
       <c r="N169">
         <v>136</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O169" s="2"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>184</v>
       </c>
@@ -8535,8 +8704,9 @@
       <c r="N170">
         <v>129</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O170" s="2"/>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>185</v>
       </c>
@@ -8579,8 +8749,9 @@
       <c r="N171">
         <v>311</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O171" s="2"/>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>186</v>
       </c>
@@ -8623,8 +8794,9 @@
       <c r="N172">
         <v>357</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O172" s="2"/>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>187</v>
       </c>
@@ -8667,8 +8839,9 @@
       <c r="N173">
         <v>271</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O173" s="2"/>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>188</v>
       </c>
@@ -8711,8 +8884,9 @@
       <c r="N174">
         <v>202</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O174" s="2"/>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>189</v>
       </c>
@@ -8755,8 +8929,9 @@
       <c r="N175">
         <v>160</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O175" s="2"/>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>191</v>
       </c>
@@ -8799,8 +8974,9 @@
       <c r="N176">
         <v>121</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O176" s="2"/>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>192</v>
       </c>
@@ -8843,8 +9019,9 @@
       <c r="N177">
         <v>89</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O177" s="2"/>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>194</v>
       </c>
@@ -8887,8 +9064,9 @@
       <c r="N178">
         <v>278</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O178" s="2"/>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>195</v>
       </c>
@@ -8931,8 +9109,9 @@
       <c r="N179">
         <v>230</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O179" s="2"/>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>196</v>
       </c>
@@ -8975,8 +9154,9 @@
       <c r="N180">
         <v>154</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O180" s="2"/>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>197</v>
       </c>
@@ -9019,8 +9199,9 @@
       <c r="N181">
         <v>108</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O181" s="2"/>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>199</v>
       </c>
@@ -9063,8 +9244,9 @@
       <c r="N182">
         <v>306</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O182" s="2"/>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>200</v>
       </c>
@@ -9107,8 +9289,9 @@
       <c r="N183">
         <v>323</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O183" s="2"/>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>201</v>
       </c>
@@ -9151,8 +9334,9 @@
       <c r="N184">
         <v>243</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O184" s="2"/>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>205</v>
       </c>
@@ -9195,8 +9379,9 @@
       <c r="N185">
         <v>479</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O185" s="2"/>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>206</v>
       </c>
@@ -9239,8 +9424,9 @@
       <c r="N186">
         <v>204</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O186" s="2"/>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>207</v>
       </c>
@@ -9283,8 +9469,9 @@
       <c r="N187">
         <v>149</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O187" s="2"/>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>208</v>
       </c>
@@ -9327,8 +9514,9 @@
       <c r="N188">
         <v>129</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O188" s="2"/>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>209</v>
       </c>
@@ -9371,8 +9559,9 @@
       <c r="N189">
         <v>139</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O189" s="2"/>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>210</v>
       </c>
@@ -9415,8 +9604,9 @@
       <c r="N190">
         <v>398</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O190" s="2"/>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>211</v>
       </c>
@@ -9459,8 +9649,9 @@
       <c r="N191">
         <v>282</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O191" s="2"/>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>212</v>
       </c>
@@ -9503,8 +9694,9 @@
       <c r="N192">
         <v>299</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O192" s="2"/>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>213</v>
       </c>
@@ -9547,8 +9739,9 @@
       <c r="N193">
         <v>321</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O193" s="2"/>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>214</v>
       </c>
@@ -9591,8 +9784,9 @@
       <c r="N194">
         <v>311</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O194" s="2"/>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>215</v>
       </c>
@@ -9635,8 +9829,9 @@
       <c r="N195">
         <v>319</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O195" s="2"/>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>216</v>
       </c>
@@ -9679,8 +9874,9 @@
       <c r="N196">
         <v>319</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O196" s="2"/>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>217</v>
       </c>
@@ -9723,8 +9919,9 @@
       <c r="N197">
         <v>277</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O197" s="2"/>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>218</v>
       </c>
@@ -9767,8 +9964,9 @@
       <c r="N198">
         <v>358</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O198" s="2"/>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>219</v>
       </c>
@@ -9811,8 +10009,9 @@
       <c r="N199">
         <v>207</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O199" s="2"/>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>220</v>
       </c>
@@ -9855,8 +10054,9 @@
       <c r="N200">
         <v>228</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O200" s="2"/>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>221</v>
       </c>
@@ -9899,8 +10099,9 @@
       <c r="N201">
         <v>265</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O201" s="2"/>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>222</v>
       </c>
@@ -9943,8 +10144,9 @@
       <c r="N202">
         <v>275</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O202" s="2"/>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>223</v>
       </c>
@@ -9987,8 +10189,9 @@
       <c r="N203">
         <v>603</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O203" s="2"/>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>224</v>
       </c>
@@ -10031,8 +10234,9 @@
       <c r="N204">
         <v>600</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O204" s="2"/>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>225</v>
       </c>
@@ -10075,8 +10279,9 @@
       <c r="N205">
         <v>489</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O205" s="2"/>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>226</v>
       </c>
@@ -10119,8 +10324,9 @@
       <c r="N206">
         <v>444</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O206" s="2"/>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>227</v>
       </c>
@@ -10163,8 +10369,9 @@
       <c r="N207">
         <v>216</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O207" s="2"/>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>228</v>
       </c>
@@ -10207,8 +10414,9 @@
       <c r="N208">
         <v>194</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O208" s="2"/>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>229</v>
       </c>
@@ -10251,8 +10459,9 @@
       <c r="N209">
         <v>145</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O209" s="2"/>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>230</v>
       </c>
@@ -10295,8 +10504,9 @@
       <c r="N210">
         <v>148</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O210" s="2"/>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>231</v>
       </c>
@@ -10339,8 +10549,9 @@
       <c r="N211">
         <v>36</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O211" s="2"/>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>232</v>
       </c>
@@ -10383,8 +10594,9 @@
       <c r="N212">
         <v>49</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O212" s="2"/>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>233</v>
       </c>
@@ -10427,8 +10639,9 @@
       <c r="N213">
         <v>57</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O213" s="2"/>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>234</v>
       </c>
@@ -10471,8 +10684,9 @@
       <c r="N214">
         <v>56</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O214" s="2"/>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>235</v>
       </c>
@@ -10515,8 +10729,9 @@
       <c r="N215">
         <v>57</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O215" s="2"/>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>236</v>
       </c>
@@ -10559,8 +10774,9 @@
       <c r="N216">
         <v>66</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O216" s="2"/>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>237</v>
       </c>
@@ -10603,8 +10819,9 @@
       <c r="N217">
         <v>71</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O217" s="2"/>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>238</v>
       </c>
@@ -10647,8 +10864,9 @@
       <c r="N218">
         <v>71</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O218" s="2"/>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>239</v>
       </c>
@@ -10691,8 +10909,9 @@
       <c r="N219">
         <v>79</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O219" s="2"/>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>240</v>
       </c>
@@ -10735,8 +10954,9 @@
       <c r="N220">
         <v>44</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O220" s="2"/>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>241</v>
       </c>
@@ -10779,8 +10999,9 @@
       <c r="N221">
         <v>55</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O221" s="2"/>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>242</v>
       </c>
@@ -10823,8 +11044,9 @@
       <c r="N222">
         <v>67</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O222" s="2"/>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>243</v>
       </c>
@@ -10867,8 +11089,9 @@
       <c r="N223">
         <v>49</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O223" s="2"/>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>244</v>
       </c>
@@ -10911,8 +11134,9 @@
       <c r="N224">
         <v>52</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O224" s="2"/>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>245</v>
       </c>
@@ -10955,8 +11179,9 @@
       <c r="N225">
         <v>85</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O225" s="2"/>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>246</v>
       </c>
@@ -10999,8 +11224,9 @@
       <c r="N226">
         <v>45</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O226" s="2"/>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>247</v>
       </c>
@@ -11043,8 +11269,9 @@
       <c r="N227">
         <v>66</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O227" s="2"/>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>248</v>
       </c>
@@ -11087,8 +11314,9 @@
       <c r="N228">
         <v>90</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O228" s="2"/>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>249</v>
       </c>
@@ -11131,8 +11359,9 @@
       <c r="N229">
         <v>97</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O229" s="2"/>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>250</v>
       </c>
@@ -11175,8 +11404,9 @@
       <c r="N230">
         <v>29</v>
       </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O230" s="2"/>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>251</v>
       </c>
@@ -11219,8 +11449,9 @@
       <c r="N231">
         <v>38</v>
       </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O231" s="2"/>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>252</v>
       </c>
@@ -11263,8 +11494,9 @@
       <c r="N232">
         <v>57</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O232" s="2"/>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>253</v>
       </c>
@@ -11307,8 +11539,9 @@
       <c r="N233">
         <v>73</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O233" s="2"/>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>254</v>
       </c>
@@ -11351,8 +11584,9 @@
       <c r="N234">
         <v>63</v>
       </c>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O234" s="2"/>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>255</v>
       </c>
@@ -11395,8 +11629,9 @@
       <c r="N235">
         <v>88</v>
       </c>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O235" s="2"/>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>256</v>
       </c>
@@ -11439,8 +11674,9 @@
       <c r="N236">
         <v>124</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O236" s="2"/>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>257</v>
       </c>
@@ -11483,8 +11719,9 @@
       <c r="N237">
         <v>126</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O237" s="2"/>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>258</v>
       </c>
@@ -11527,8 +11764,9 @@
       <c r="N238">
         <v>194</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O238" s="2"/>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>259</v>
       </c>
@@ -11571,8 +11809,9 @@
       <c r="N239">
         <v>176</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O239" s="2"/>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>260</v>
       </c>
@@ -11615,8 +11854,9 @@
       <c r="N240">
         <v>194</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O240" s="2"/>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>261</v>
       </c>
@@ -11659,8 +11899,9 @@
       <c r="N241">
         <v>194</v>
       </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O241" s="2"/>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>262</v>
       </c>
@@ -11703,8 +11944,9 @@
       <c r="N242">
         <v>165</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O242" s="2"/>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>263</v>
       </c>
@@ -11747,8 +11989,9 @@
       <c r="N243">
         <v>165</v>
       </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O243" s="2"/>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>265</v>
       </c>
@@ -11791,8 +12034,9 @@
       <c r="N244">
         <v>825</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O244" s="2"/>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>266</v>
       </c>
@@ -11835,8 +12079,9 @@
       <c r="N245">
         <v>390</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O245" s="2"/>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>267</v>
       </c>
@@ -11879,8 +12124,9 @@
       <c r="N246">
         <v>365</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O246" s="2"/>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>268</v>
       </c>
@@ -11923,8 +12169,9 @@
       <c r="N247">
         <v>117</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O247" s="2"/>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>269</v>
       </c>
@@ -11967,8 +12214,9 @@
       <c r="N248">
         <v>105</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O248" s="2"/>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>270</v>
       </c>
@@ -12011,8 +12259,9 @@
       <c r="N249">
         <v>105</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O249" s="2"/>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>271</v>
       </c>
@@ -12055,8 +12304,9 @@
       <c r="N250">
         <v>197</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O250" s="2"/>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>272</v>
       </c>
@@ -12099,8 +12349,9 @@
       <c r="N251">
         <v>123</v>
       </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O251" s="2"/>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>273</v>
       </c>
@@ -12143,8 +12394,9 @@
       <c r="N252">
         <v>214</v>
       </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O252" s="2"/>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>274</v>
       </c>
@@ -12187,8 +12439,9 @@
       <c r="N253">
         <v>154</v>
       </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O253" s="2"/>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>275</v>
       </c>
@@ -12231,8 +12484,9 @@
       <c r="N254">
         <v>214</v>
       </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O254" s="2"/>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>276</v>
       </c>
@@ -12275,8 +12529,9 @@
       <c r="N255">
         <v>248</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O255" s="2"/>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>277</v>
       </c>
@@ -12319,8 +12574,9 @@
       <c r="N256">
         <v>190</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O256" s="2"/>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>278</v>
       </c>
@@ -12363,8 +12619,9 @@
       <c r="N257">
         <v>236</v>
       </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O257" s="2"/>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>279</v>
       </c>
@@ -12407,8 +12664,9 @@
       <c r="N258">
         <v>248</v>
       </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O258" s="2"/>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>280</v>
       </c>
@@ -12451,8 +12709,9 @@
       <c r="N259">
         <v>262</v>
       </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O259" s="2"/>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>281</v>
       </c>
@@ -12495,8 +12754,9 @@
       <c r="N260">
         <v>170</v>
       </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O260" s="2"/>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>282</v>
       </c>
@@ -12539,8 +12799,9 @@
       <c r="N261">
         <v>280</v>
       </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O261" s="2"/>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>283</v>
       </c>
@@ -12583,8 +12844,9 @@
       <c r="N262">
         <v>265</v>
       </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O262" s="2"/>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>284</v>
       </c>
@@ -12627,8 +12889,9 @@
       <c r="N263">
         <v>285</v>
       </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O263" s="2"/>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>285</v>
       </c>
@@ -12671,8 +12934,9 @@
       <c r="N264">
         <v>285</v>
       </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O264" s="2"/>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>286</v>
       </c>
@@ -12715,8 +12979,9 @@
       <c r="N265">
         <v>197</v>
       </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O265" s="2"/>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>287</v>
       </c>
@@ -12759,8 +13024,9 @@
       <c r="N266">
         <v>227</v>
       </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O266" s="2"/>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>288</v>
       </c>
@@ -12803,8 +13069,9 @@
       <c r="N267">
         <v>235</v>
       </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O267" s="2"/>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>289</v>
       </c>
@@ -12847,8 +13114,9 @@
       <c r="N268">
         <v>185</v>
       </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O268" s="2"/>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>290</v>
       </c>
@@ -12891,8 +13159,9 @@
       <c r="N269">
         <v>338</v>
       </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O269" s="2"/>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>291</v>
       </c>
@@ -12935,8 +13204,9 @@
       <c r="N270">
         <v>172</v>
       </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O270" s="2"/>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>292</v>
       </c>
@@ -12979,8 +13249,9 @@
       <c r="N271">
         <v>284</v>
       </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O271" s="2"/>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>293</v>
       </c>
@@ -13023,8 +13294,9 @@
       <c r="N272">
         <v>421</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O272" s="2"/>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>294</v>
       </c>
@@ -13067,8 +13339,9 @@
       <c r="N273">
         <v>182</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O273" s="2"/>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>295</v>
       </c>
@@ -13111,8 +13384,9 @@
       <c r="N274">
         <v>221</v>
       </c>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O274" s="2"/>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>296</v>
       </c>
@@ -13155,8 +13429,9 @@
       <c r="N275">
         <v>109</v>
       </c>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O275" s="2"/>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>297</v>
       </c>
@@ -13199,8 +13474,9 @@
       <c r="N276">
         <v>623</v>
       </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O276" s="2"/>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>298</v>
       </c>
@@ -13243,8 +13519,9 @@
       <c r="N277">
         <v>368</v>
       </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O277" s="2"/>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>299</v>
       </c>
@@ -13287,8 +13564,9 @@
       <c r="N278">
         <v>451</v>
       </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O278" s="2"/>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>300</v>
       </c>
@@ -13331,8 +13609,9 @@
       <c r="N279">
         <v>1099</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O279" s="2"/>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>302</v>
       </c>
@@ -13375,8 +13654,9 @@
       <c r="N280">
         <v>280</v>
       </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O280" s="2"/>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>303</v>
       </c>
@@ -13419,8 +13699,9 @@
       <c r="N281">
         <v>480</v>
       </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O281" s="2"/>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>304</v>
       </c>
@@ -13463,8 +13744,9 @@
       <c r="N282">
         <v>198</v>
       </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O282" s="2"/>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>305</v>
       </c>
@@ -13507,8 +13789,9 @@
       <c r="N283">
         <v>222</v>
       </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O283" s="2"/>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>306</v>
       </c>
@@ -13551,8 +13834,9 @@
       <c r="N284">
         <v>4915</v>
       </c>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O284" s="2"/>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>307</v>
       </c>
@@ -13595,8 +13879,9 @@
       <c r="N285">
         <v>626</v>
       </c>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O285" s="2"/>
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>308</v>
       </c>
@@ -13639,8 +13924,9 @@
       <c r="N286">
         <v>183</v>
       </c>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O286" s="2"/>
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>309</v>
       </c>
@@ -13683,8 +13969,9 @@
       <c r="N287">
         <v>281</v>
       </c>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O287" s="2"/>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>310</v>
       </c>
@@ -13727,8 +14014,9 @@
       <c r="N288">
         <v>288</v>
       </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O288" s="2"/>
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>311</v>
       </c>
@@ -13771,8 +14059,9 @@
       <c r="N289">
         <v>324</v>
       </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O289" s="2"/>
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>312</v>
       </c>
@@ -13815,8 +14104,9 @@
       <c r="N290">
         <v>628</v>
       </c>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O290" s="2"/>
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>315</v>
       </c>
@@ -13859,8 +14149,9 @@
       <c r="N291">
         <v>464</v>
       </c>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O291" s="2"/>
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>316</v>
       </c>
@@ -13903,8 +14194,9 @@
       <c r="N292">
         <v>440</v>
       </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O292" s="2"/>
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>319</v>
       </c>
@@ -13947,8 +14239,9 @@
       <c r="N293">
         <v>579</v>
       </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O293" s="2"/>
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>320</v>
       </c>
@@ -13991,8 +14284,9 @@
       <c r="N294">
         <v>580</v>
       </c>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O294" s="2"/>
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>321</v>
       </c>
@@ -14035,8 +14329,9 @@
       <c r="N295">
         <v>34</v>
       </c>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O295" s="2"/>
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>322</v>
       </c>
@@ -14079,8 +14374,9 @@
       <c r="N296">
         <v>31</v>
       </c>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O296" s="2"/>
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>323</v>
       </c>
@@ -14123,8 +14419,9 @@
       <c r="N297">
         <v>362</v>
       </c>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O297" s="2"/>
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>324</v>
       </c>
@@ -14167,8 +14464,9 @@
       <c r="N298">
         <v>184</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O298" s="2"/>
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>325</v>
       </c>
@@ -14211,8 +14509,9 @@
       <c r="N299">
         <v>183</v>
       </c>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O299" s="2"/>
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>326</v>
       </c>
@@ -14255,8 +14554,9 @@
       <c r="N300">
         <v>661</v>
       </c>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O300" s="2"/>
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>327</v>
       </c>
@@ -14299,8 +14599,9 @@
       <c r="N301">
         <v>558</v>
       </c>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O301" s="2"/>
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>328</v>
       </c>
@@ -14343,8 +14644,9 @@
       <c r="N302">
         <v>43</v>
       </c>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O302" s="2"/>
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>329</v>
       </c>
@@ -14387,8 +14689,9 @@
       <c r="N303">
         <v>47</v>
       </c>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O303" s="2"/>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>330</v>
       </c>
@@ -14431,8 +14734,9 @@
       <c r="N304">
         <v>51</v>
       </c>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O304" s="2"/>
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>331</v>
       </c>
@@ -14475,8 +14779,9 @@
       <c r="N305">
         <v>58</v>
       </c>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O305" s="2"/>
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>332</v>
       </c>
@@ -14519,8 +14824,9 @@
       <c r="N306">
         <v>78</v>
       </c>
-    </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O306" s="2"/>
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>333</v>
       </c>
@@ -14563,8 +14869,9 @@
       <c r="N307">
         <v>90</v>
       </c>
-    </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O307" s="2"/>
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>334</v>
       </c>
@@ -14607,8 +14914,9 @@
       <c r="N308">
         <v>50</v>
       </c>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O308" s="2"/>
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>335</v>
       </c>
@@ -14651,8 +14959,9 @@
       <c r="N309">
         <v>69</v>
       </c>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O309" s="2"/>
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>336</v>
       </c>
@@ -14695,8 +15004,9 @@
       <c r="N310">
         <v>96</v>
       </c>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O310" s="2"/>
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>337</v>
       </c>
@@ -14739,8 +15049,9 @@
       <c r="N311">
         <v>114</v>
       </c>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O311" s="2"/>
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>338</v>
       </c>
@@ -14783,8 +15094,9 @@
       <c r="N312">
         <v>39</v>
       </c>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O312" s="2"/>
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>339</v>
       </c>
@@ -14827,8 +15139,9 @@
       <c r="N313">
         <v>73</v>
       </c>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O313" s="2"/>
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>340</v>
       </c>
@@ -14871,8 +15184,9 @@
       <c r="N314">
         <v>101</v>
       </c>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O314" s="2"/>
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>341</v>
       </c>
@@ -14915,8 +15229,9 @@
       <c r="N315">
         <v>80</v>
       </c>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O315" s="2"/>
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>342</v>
       </c>
@@ -14959,8 +15274,9 @@
       <c r="N316">
         <v>97</v>
       </c>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O316" s="2"/>
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>343</v>
       </c>
@@ -15003,8 +15319,9 @@
       <c r="N317">
         <v>320</v>
       </c>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O317" s="2"/>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>344</v>
       </c>
@@ -15047,8 +15364,9 @@
       <c r="N318">
         <v>314</v>
       </c>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O318" s="2"/>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>345</v>
       </c>
@@ -15091,8 +15409,9 @@
       <c r="N319">
         <v>315</v>
       </c>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O319" s="2"/>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>348</v>
       </c>
@@ -15135,8 +15454,9 @@
       <c r="N320">
         <v>61</v>
       </c>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O320" s="2"/>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>350</v>
       </c>
@@ -15179,8 +15499,9 @@
       <c r="N321">
         <v>88</v>
       </c>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O321" s="2"/>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>351</v>
       </c>
@@ -15223,8 +15544,9 @@
       <c r="N322">
         <v>87</v>
       </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O322" s="2"/>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>353</v>
       </c>
@@ -15267,8 +15589,9 @@
       <c r="N323">
         <v>83</v>
       </c>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O323" s="2"/>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>358</v>
       </c>
@@ -15311,8 +15634,9 @@
       <c r="N324">
         <v>83</v>
       </c>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O324" s="2"/>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>359</v>
       </c>
@@ -15355,8 +15679,9 @@
       <c r="N325">
         <v>70</v>
       </c>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O325" s="2"/>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>360</v>
       </c>
@@ -15399,8 +15724,9 @@
       <c r="N326">
         <v>81</v>
       </c>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O326" s="2"/>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>361</v>
       </c>
@@ -15443,8 +15769,9 @@
       <c r="N327">
         <v>82</v>
       </c>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O327" s="2"/>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>362</v>
       </c>
@@ -15487,8 +15814,9 @@
       <c r="N328">
         <v>79</v>
       </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O328" s="2"/>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>363</v>
       </c>
@@ -15531,8 +15859,9 @@
       <c r="N329">
         <v>71</v>
       </c>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O329" s="2"/>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>364</v>
       </c>
@@ -15575,8 +15904,9 @@
       <c r="N330">
         <v>82</v>
       </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O330" s="2"/>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>365</v>
       </c>
@@ -15619,8 +15949,9 @@
       <c r="N331">
         <v>83</v>
       </c>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O331" s="2"/>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>366</v>
       </c>
@@ -15663,8 +15994,9 @@
       <c r="N332">
         <v>84</v>
       </c>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O332" s="2"/>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>367</v>
       </c>
@@ -15707,8 +16039,9 @@
       <c r="N333">
         <v>83</v>
       </c>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O333" s="2"/>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>368</v>
       </c>
@@ -15751,8 +16084,9 @@
       <c r="N334">
         <v>77</v>
       </c>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O334" s="2"/>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>369</v>
       </c>
@@ -15795,8 +16129,9 @@
       <c r="N335">
         <v>75</v>
       </c>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O335" s="2"/>
+    </row>
+    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>370</v>
       </c>
@@ -15839,8 +16174,9 @@
       <c r="N336">
         <v>74</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O336" s="2"/>
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>371</v>
       </c>
@@ -15883,8 +16219,9 @@
       <c r="N337">
         <v>1662</v>
       </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O337" s="2"/>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>372</v>
       </c>
@@ -15927,8 +16264,9 @@
       <c r="N338">
         <v>334</v>
       </c>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O338" s="2"/>
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>373</v>
       </c>
@@ -15971,8 +16309,9 @@
       <c r="N339">
         <v>266</v>
       </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O339" s="2"/>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>374</v>
       </c>
@@ -16015,8 +16354,9 @@
       <c r="N340">
         <v>113</v>
       </c>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O340" s="2"/>
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>375</v>
       </c>
@@ -16059,8 +16399,9 @@
       <c r="N341">
         <v>123</v>
       </c>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O341" s="2"/>
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>377</v>
       </c>
@@ -16103,8 +16444,9 @@
       <c r="N342">
         <v>339</v>
       </c>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O342" s="2"/>
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>378</v>
       </c>
@@ -16147,8 +16489,9 @@
       <c r="N343">
         <v>301</v>
       </c>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O343" s="2"/>
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>379</v>
       </c>
@@ -16191,8 +16534,9 @@
       <c r="N344">
         <v>254</v>
       </c>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O344" s="2"/>
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>380</v>
       </c>
@@ -16235,8 +16579,9 @@
       <c r="N345">
         <v>339</v>
       </c>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O345" s="2"/>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>382</v>
       </c>
@@ -16279,8 +16624,9 @@
       <c r="N346">
         <v>411</v>
       </c>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O346" s="2"/>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>383</v>
       </c>
@@ -16323,8 +16669,9 @@
       <c r="N347">
         <v>422</v>
       </c>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O347" s="2"/>
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>384</v>
       </c>
@@ -16367,8 +16714,9 @@
       <c r="N348">
         <v>411</v>
       </c>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O348" s="2"/>
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>385</v>
       </c>
@@ -16411,8 +16759,9 @@
       <c r="N349">
         <v>431</v>
       </c>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O349" s="2"/>
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>386</v>
       </c>
@@ -16455,8 +16804,9 @@
       <c r="N350">
         <v>242</v>
       </c>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O350" s="2"/>
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>387</v>
       </c>
@@ -16499,8 +16849,9 @@
       <c r="N351">
         <v>330</v>
       </c>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O351" s="2"/>
+    </row>
+    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>388</v>
       </c>
@@ -16543,8 +16894,9 @@
       <c r="N352">
         <v>292</v>
       </c>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O352" s="2"/>
+    </row>
+    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>389</v>
       </c>
@@ -16587,8 +16939,9 @@
       <c r="N353">
         <v>322</v>
       </c>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O353" s="2"/>
+    </row>
+    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>390</v>
       </c>
@@ -16631,8 +16984,9 @@
       <c r="N354">
         <v>292</v>
       </c>
-    </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O354" s="2"/>
+    </row>
+    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>391</v>
       </c>
@@ -16675,8 +17029,9 @@
       <c r="N355">
         <v>254</v>
       </c>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O355" s="2"/>
+    </row>
+    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>392</v>
       </c>
@@ -16719,8 +17074,9 @@
       <c r="N356">
         <v>335</v>
       </c>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O356" s="2"/>
+    </row>
+    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>393</v>
       </c>
@@ -16763,8 +17119,9 @@
       <c r="N357">
         <v>531</v>
       </c>
-    </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O357" s="2"/>
+    </row>
+    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>394</v>
       </c>
@@ -16807,8 +17164,9 @@
       <c r="N358">
         <v>377</v>
       </c>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O358" s="2"/>
+    </row>
+    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>395</v>
       </c>
@@ -16851,8 +17209,9 @@
       <c r="N359">
         <v>394</v>
       </c>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O359" s="2"/>
+    </row>
+    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>396</v>
       </c>
@@ -16895,8 +17254,9 @@
       <c r="N360">
         <v>216</v>
       </c>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O360" s="2"/>
+    </row>
+    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>397</v>
       </c>
@@ -16939,8 +17299,9 @@
       <c r="N361">
         <v>257</v>
       </c>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O361" s="2"/>
+    </row>
+    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>398</v>
       </c>
@@ -16983,8 +17344,9 @@
       <c r="N362">
         <v>301</v>
       </c>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O362" s="2"/>
+    </row>
+    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>399</v>
       </c>
@@ -17027,8 +17389,9 @@
       <c r="N363">
         <v>196</v>
       </c>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O363" s="2"/>
+    </row>
+    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>400</v>
       </c>
@@ -17071,8 +17434,9 @@
       <c r="N364">
         <v>283</v>
       </c>
-    </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O364" s="2"/>
+    </row>
+    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>401</v>
       </c>
@@ -17115,8 +17479,9 @@
       <c r="N365">
         <v>397</v>
       </c>
-    </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O365" s="2"/>
+    </row>
+    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>402</v>
       </c>
@@ -17159,8 +17524,9 @@
       <c r="N366">
         <v>184</v>
       </c>
-    </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O366" s="2"/>
+    </row>
+    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>403</v>
       </c>
@@ -17203,8 +17569,9 @@
       <c r="N367">
         <v>211</v>
       </c>
-    </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O367" s="2"/>
+    </row>
+    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>404</v>
       </c>
@@ -17247,8 +17614,9 @@
       <c r="N368">
         <v>165</v>
       </c>
-    </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O368" s="2"/>
+    </row>
+    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>411</v>
       </c>
@@ -17291,8 +17659,9 @@
       <c r="N369">
         <v>181</v>
       </c>
-    </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O369" s="2"/>
+    </row>
+    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>412</v>
       </c>
@@ -17335,8 +17704,9 @@
       <c r="N370">
         <v>245</v>
       </c>
-    </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O370" s="2"/>
+    </row>
+    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>413</v>
       </c>
@@ -17379,8 +17749,9 @@
       <c r="N371">
         <v>162</v>
       </c>
-    </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O371" s="2"/>
+    </row>
+    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>414</v>
       </c>
@@ -17423,8 +17794,9 @@
       <c r="N372">
         <v>215</v>
       </c>
-    </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O372" s="2"/>
+    </row>
+    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>415</v>
       </c>
@@ -17467,8 +17839,9 @@
       <c r="N373">
         <v>307</v>
       </c>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O373" s="2"/>
+    </row>
+    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>416</v>
       </c>
@@ -17511,8 +17884,9 @@
       <c r="N374">
         <v>239</v>
       </c>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O374" s="2"/>
+    </row>
+    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>417</v>
       </c>
@@ -17555,8 +17929,9 @@
       <c r="N375">
         <v>152</v>
       </c>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O375" s="2"/>
+    </row>
+    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>418</v>
       </c>
@@ -17599,8 +17974,9 @@
       <c r="N376">
         <v>244</v>
       </c>
-    </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O376" s="2"/>
+    </row>
+    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>419</v>
       </c>
@@ -17643,8 +18019,9 @@
       <c r="N377">
         <v>240</v>
       </c>
-    </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O377" s="2"/>
+    </row>
+    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>420</v>
       </c>
@@ -17687,8 +18064,9 @@
       <c r="N378">
         <v>201</v>
       </c>
-    </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O378" s="2"/>
+    </row>
+    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>421</v>
       </c>
@@ -17731,8 +18109,9 @@
       <c r="N379">
         <v>117</v>
       </c>
-    </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O379" s="2"/>
+    </row>
+    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>422</v>
       </c>
@@ -17775,8 +18154,9 @@
       <c r="N380">
         <v>98</v>
       </c>
-    </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O380" s="2"/>
+    </row>
+    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>423</v>
       </c>
@@ -17819,8 +18199,9 @@
       <c r="N381">
         <v>64</v>
       </c>
-    </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O381" s="2"/>
+    </row>
+    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>424</v>
       </c>
@@ -17863,8 +18244,9 @@
       <c r="N382">
         <v>83</v>
       </c>
-    </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O382" s="2"/>
+    </row>
+    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>425</v>
       </c>
@@ -17907,8 +18289,9 @@
       <c r="N383">
         <v>78</v>
       </c>
-    </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O383" s="2"/>
+    </row>
+    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>426</v>
       </c>
@@ -17951,8 +18334,9 @@
       <c r="N384">
         <v>88</v>
       </c>
-    </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O384" s="2"/>
+    </row>
+    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>427</v>
       </c>
@@ -17995,8 +18379,9 @@
       <c r="N385">
         <v>88</v>
       </c>
-    </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O385" s="2"/>
+    </row>
+    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>428</v>
       </c>
@@ -18039,8 +18424,9 @@
       <c r="N386">
         <v>71</v>
       </c>
-    </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O386" s="2"/>
+    </row>
+    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>429</v>
       </c>
@@ -18083,8 +18469,9 @@
       <c r="N387">
         <v>105</v>
       </c>
-    </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O387" s="2"/>
+    </row>
+    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>430</v>
       </c>
@@ -18127,8 +18514,9 @@
       <c r="N388">
         <v>136</v>
       </c>
-    </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O388" s="2"/>
+    </row>
+    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>431</v>
       </c>
@@ -18171,8 +18559,9 @@
       <c r="N389">
         <v>371</v>
       </c>
-    </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O389" s="2"/>
+    </row>
+    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>432</v>
       </c>
@@ -18215,8 +18604,9 @@
       <c r="N390">
         <v>389</v>
       </c>
-    </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O390" s="2"/>
+    </row>
+    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>433</v>
       </c>
@@ -18259,8 +18649,9 @@
       <c r="N391">
         <v>392</v>
       </c>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O391" s="2"/>
+    </row>
+    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>434</v>
       </c>
@@ -18303,8 +18694,9 @@
       <c r="N392">
         <v>356</v>
       </c>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O392" s="2"/>
+    </row>
+    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>435</v>
       </c>
@@ -18347,8 +18739,9 @@
       <c r="N393">
         <v>364</v>
       </c>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O393" s="2"/>
+    </row>
+    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>436</v>
       </c>
@@ -18391,8 +18784,9 @@
       <c r="N394">
         <v>378</v>
       </c>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O394" s="2"/>
+    </row>
+    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>437</v>
       </c>
@@ -18435,8 +18829,9 @@
       <c r="N395">
         <v>334</v>
       </c>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O395" s="2"/>
+    </row>
+    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>438</v>
       </c>
@@ -18479,8 +18874,9 @@
       <c r="N396">
         <v>374</v>
       </c>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O396" s="2"/>
+    </row>
+    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>439</v>
       </c>
@@ -18523,8 +18919,9 @@
       <c r="N397">
         <v>311</v>
       </c>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O397" s="2"/>
+    </row>
+    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>440</v>
       </c>
@@ -18567,8 +18964,9 @@
       <c r="N398">
         <v>343</v>
       </c>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O398" s="2"/>
+    </row>
+    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>441</v>
       </c>
@@ -18611,8 +19009,9 @@
       <c r="N399">
         <v>378</v>
       </c>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O399" s="2"/>
+    </row>
+    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>442</v>
       </c>
@@ -18655,8 +19054,9 @@
       <c r="N400">
         <v>394</v>
       </c>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O400" s="2"/>
+    </row>
+    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>443</v>
       </c>
@@ -18699,8 +19099,9 @@
       <c r="N401">
         <v>311</v>
       </c>
-    </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O401" s="2"/>
+    </row>
+    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>444</v>
       </c>
@@ -18743,8 +19144,9 @@
       <c r="N402">
         <v>433</v>
       </c>
-    </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O402" s="2"/>
+    </row>
+    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>445</v>
       </c>
@@ -18787,8 +19189,9 @@
       <c r="N403">
         <v>255</v>
       </c>
-    </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O403" s="2"/>
+    </row>
+    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>446</v>
       </c>
@@ -18831,8 +19234,9 @@
       <c r="N404">
         <v>275</v>
       </c>
-    </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O404" s="2"/>
+    </row>
+    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>447</v>
       </c>
@@ -18875,8 +19279,9 @@
       <c r="N405">
         <v>334</v>
       </c>
-    </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O405" s="2"/>
+    </row>
+    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>448</v>
       </c>
@@ -18919,8 +19324,9 @@
       <c r="N406">
         <v>332</v>
       </c>
-    </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O406" s="2"/>
+    </row>
+    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>449</v>
       </c>
@@ -18963,8 +19369,9 @@
       <c r="N407">
         <v>430</v>
       </c>
-    </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O407" s="2"/>
+    </row>
+    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>450</v>
       </c>
@@ -19007,8 +19414,9 @@
       <c r="N408">
         <v>408</v>
       </c>
-    </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O408" s="2"/>
+    </row>
+    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>451</v>
       </c>
@@ -19051,8 +19459,9 @@
       <c r="N409">
         <v>491</v>
       </c>
-    </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O409" s="2"/>
+    </row>
+    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>452</v>
       </c>
@@ -19095,8 +19504,9 @@
       <c r="N410">
         <v>540</v>
       </c>
-    </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O410" s="2"/>
+    </row>
+    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>453</v>
       </c>
@@ -19139,8 +19549,9 @@
       <c r="N411">
         <v>258</v>
       </c>
-    </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O411" s="2"/>
+    </row>
+    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>454</v>
       </c>
@@ -19183,8 +19594,9 @@
       <c r="N412">
         <v>258</v>
       </c>
-    </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O412" s="2"/>
+    </row>
+    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>455</v>
       </c>
@@ -19227,8 +19639,9 @@
       <c r="N413">
         <v>332</v>
       </c>
-    </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O413" s="2"/>
+    </row>
+    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>456</v>
       </c>
@@ -19271,8 +19684,9 @@
       <c r="N414">
         <v>332</v>
       </c>
-    </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O414" s="2"/>
+    </row>
+    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>457</v>
       </c>
@@ -19315,8 +19729,9 @@
       <c r="N415">
         <v>94</v>
       </c>
-    </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O415" s="2"/>
+    </row>
+    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>458</v>
       </c>
@@ -19359,8 +19774,9 @@
       <c r="N416">
         <v>104</v>
       </c>
-    </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O416" s="2"/>
+    </row>
+    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>459</v>
       </c>
@@ -19403,8 +19819,9 @@
       <c r="N417">
         <v>98</v>
       </c>
-    </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O417" s="2"/>
+    </row>
+    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>460</v>
       </c>
@@ -19447,8 +19864,9 @@
       <c r="N418">
         <v>104</v>
       </c>
-    </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O418" s="2"/>
+    </row>
+    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>461</v>
       </c>
@@ -19491,8 +19909,9 @@
       <c r="N419">
         <v>82</v>
       </c>
-    </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O419" s="2"/>
+    </row>
+    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>462</v>
       </c>
@@ -19535,8 +19954,9 @@
       <c r="N420">
         <v>82</v>
       </c>
-    </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O420" s="2"/>
+    </row>
+    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>463</v>
       </c>
@@ -19579,8 +19999,9 @@
       <c r="N421">
         <v>113</v>
       </c>
-    </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O421" s="2"/>
+    </row>
+    <row r="422" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>464</v>
       </c>
@@ -19623,8 +20044,9 @@
       <c r="N422">
         <v>100</v>
       </c>
-    </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O422" s="2"/>
+    </row>
+    <row r="423" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>465</v>
       </c>
@@ -19667,8 +20089,9 @@
       <c r="N423">
         <v>118</v>
       </c>
-    </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O423" s="2"/>
+    </row>
+    <row r="424" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>466</v>
       </c>
@@ -19711,8 +20134,9 @@
       <c r="N424">
         <v>181</v>
       </c>
-    </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O424" s="2"/>
+    </row>
+    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>467</v>
       </c>
@@ -19755,8 +20179,9 @@
       <c r="N425">
         <v>152</v>
       </c>
-    </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O425" s="2"/>
+    </row>
+    <row r="426" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>468</v>
       </c>
@@ -19799,8 +20224,9 @@
       <c r="N426">
         <v>245</v>
       </c>
-    </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O426" s="2"/>
+    </row>
+    <row r="427" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>469</v>
       </c>
@@ -19843,8 +20269,9 @@
       <c r="N427">
         <v>245</v>
       </c>
-    </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O427" s="2"/>
+    </row>
+    <row r="428" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>470</v>
       </c>
@@ -19887,8 +20314,9 @@
       <c r="N428">
         <v>302</v>
       </c>
-    </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O428" s="2"/>
+    </row>
+    <row r="429" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>471</v>
       </c>
@@ -19931,8 +20359,9 @@
       <c r="N429">
         <v>365</v>
       </c>
-    </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O429" s="2"/>
+    </row>
+    <row r="430" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>472</v>
       </c>
@@ -19975,8 +20404,9 @@
       <c r="N430">
         <v>356</v>
       </c>
-    </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O430" s="2"/>
+    </row>
+    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>473</v>
       </c>
@@ -20019,8 +20449,9 @@
       <c r="N431">
         <v>351</v>
       </c>
-    </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O431" s="2"/>
+    </row>
+    <row r="432" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>474</v>
       </c>
@@ -20063,8 +20494,9 @@
       <c r="N432">
         <v>356</v>
       </c>
-    </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O432" s="2"/>
+    </row>
+    <row r="433" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>475</v>
       </c>
@@ -20107,8 +20539,9 @@
       <c r="N433">
         <v>334</v>
       </c>
-    </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O433" s="2"/>
+    </row>
+    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>476</v>
       </c>
@@ -20151,8 +20584,9 @@
       <c r="N434">
         <v>400</v>
       </c>
-    </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O434" s="2"/>
+    </row>
+    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>477</v>
       </c>
@@ -20195,8 +20629,9 @@
       <c r="N435">
         <v>467</v>
       </c>
-    </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O435" s="2"/>
+    </row>
+    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>478</v>
       </c>
@@ -20239,8 +20674,9 @@
       <c r="N436">
         <v>512</v>
       </c>
-    </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O436" s="2"/>
+    </row>
+    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>479</v>
       </c>
@@ -20283,8 +20719,9 @@
       <c r="N437">
         <v>356</v>
       </c>
-    </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O437" s="2"/>
+    </row>
+    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>480</v>
       </c>
@@ -20327,8 +20764,9 @@
       <c r="N438">
         <v>445</v>
       </c>
-    </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O438" s="2"/>
+    </row>
+    <row r="439" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>481</v>
       </c>
@@ -20371,8 +20809,9 @@
       <c r="N439">
         <v>534</v>
       </c>
-    </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O439" s="2"/>
+    </row>
+    <row r="440" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>482</v>
       </c>
@@ -20415,8 +20854,9 @@
       <c r="N440">
         <v>547</v>
       </c>
-    </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O440" s="2"/>
+    </row>
+    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>483</v>
       </c>
@@ -20459,8 +20899,9 @@
       <c r="N441">
         <v>400</v>
       </c>
-    </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O441" s="2"/>
+    </row>
+    <row r="442" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>484</v>
       </c>
@@ -20503,8 +20944,9 @@
       <c r="N442">
         <v>534</v>
       </c>
-    </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O442" s="2"/>
+    </row>
+    <row r="443" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>485</v>
       </c>
@@ -20547,8 +20989,9 @@
       <c r="N443">
         <v>498</v>
       </c>
-    </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O443" s="2"/>
+    </row>
+    <row r="444" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>486</v>
       </c>
@@ -20591,8 +21034,9 @@
       <c r="N444">
         <v>400</v>
       </c>
-    </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O444" s="2"/>
+    </row>
+    <row r="445" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>487</v>
       </c>
@@ -20635,8 +21079,9 @@
       <c r="N445">
         <v>436</v>
       </c>
-    </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O445" s="2"/>
+    </row>
+    <row r="446" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>488</v>
       </c>
@@ -20679,8 +21124,9 @@
       <c r="N446">
         <v>445</v>
       </c>
-    </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O446" s="2"/>
+    </row>
+    <row r="447" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>489</v>
       </c>
@@ -20723,8 +21169,9 @@
       <c r="N447">
         <v>489</v>
       </c>
-    </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O447" s="2"/>
+    </row>
+    <row r="448" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>494</v>
       </c>
@@ -20767,8 +21214,9 @@
       <c r="N448">
         <v>505</v>
       </c>
-    </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O448" s="2"/>
+    </row>
+    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>495</v>
       </c>
@@ -20811,8 +21259,9 @@
       <c r="N449">
         <v>329</v>
       </c>
-    </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O449" s="2"/>
+    </row>
+    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>496</v>
       </c>
@@ -20855,8 +21304,9 @@
       <c r="N450">
         <v>578</v>
       </c>
-    </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O450" s="2"/>
+    </row>
+    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>497</v>
       </c>
@@ -20899,8 +21349,9 @@
       <c r="N451">
         <v>183</v>
       </c>
-    </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O451" s="2"/>
+    </row>
+    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>498</v>
       </c>
@@ -20943,8 +21394,9 @@
       <c r="N452">
         <v>177</v>
       </c>
-    </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O452" s="2"/>
+    </row>
+    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>499</v>
       </c>
@@ -20987,8 +21439,9 @@
       <c r="N453">
         <v>172</v>
       </c>
-    </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O453" s="2"/>
+    </row>
+    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>500</v>
       </c>
@@ -21031,8 +21484,9 @@
       <c r="N454">
         <v>177</v>
       </c>
-    </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O454" s="2"/>
+    </row>
+    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>501</v>
       </c>
@@ -21075,8 +21529,9 @@
       <c r="N455">
         <v>198</v>
       </c>
-    </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O455" s="2"/>
+    </row>
+    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>502</v>
       </c>
@@ -21119,8 +21574,9 @@
       <c r="N456">
         <v>183</v>
       </c>
-    </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O456" s="2"/>
+    </row>
+    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>503</v>
       </c>
@@ -21163,8 +21619,9 @@
       <c r="N457">
         <v>187</v>
       </c>
-    </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O457" s="2"/>
+    </row>
+    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>504</v>
       </c>
@@ -21207,8 +21664,9 @@
       <c r="N458">
         <v>151</v>
       </c>
-    </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O458" s="2"/>
+    </row>
+    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>505</v>
       </c>
@@ -21251,8 +21709,9 @@
       <c r="N459">
         <v>166</v>
       </c>
-    </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O459" s="2"/>
+    </row>
+    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>506</v>
       </c>
@@ -21295,8 +21754,9 @@
       <c r="N460">
         <v>201</v>
       </c>
-    </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O460" s="2"/>
+    </row>
+    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>507</v>
       </c>
@@ -21339,8 +21799,9 @@
       <c r="N461">
         <v>198</v>
       </c>
-    </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O461" s="2"/>
+    </row>
+    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>508</v>
       </c>
@@ -21383,8 +21844,9 @@
       <c r="N462">
         <v>200</v>
       </c>
-    </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O462" s="2"/>
+    </row>
+    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>509</v>
       </c>
@@ -21427,8 +21889,9 @@
       <c r="N463">
         <v>199</v>
       </c>
-    </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O463" s="2"/>
+    </row>
+    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>510</v>
       </c>
@@ -21471,8 +21934,9 @@
       <c r="N464">
         <v>220</v>
       </c>
-    </row>
-    <row r="465" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O464" s="2"/>
+    </row>
+    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>511</v>
       </c>
@@ -21515,8 +21979,9 @@
       <c r="N465">
         <v>216</v>
       </c>
-    </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O465" s="2"/>
+    </row>
+    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>512</v>
       </c>
@@ -21559,8 +22024,9 @@
       <c r="N466">
         <v>243</v>
       </c>
-    </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O466" s="2"/>
+    </row>
+    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>513</v>
       </c>
@@ -21603,8 +22069,9 @@
       <c r="N467">
         <v>243</v>
       </c>
-    </row>
-    <row r="468" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O467" s="2"/>
+    </row>
+    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>514</v>
       </c>
@@ -21647,8 +22114,9 @@
       <c r="N468">
         <v>249</v>
       </c>
-    </row>
-    <row r="469" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O468" s="2"/>
+    </row>
+    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>515</v>
       </c>
@@ -21691,8 +22159,9 @@
       <c r="N469">
         <v>239</v>
       </c>
-    </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O469" s="2"/>
+    </row>
+    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>516</v>
       </c>
@@ -21735,8 +22204,9 @@
       <c r="N470">
         <v>203</v>
       </c>
-    </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O470" s="2"/>
+    </row>
+    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>517</v>
       </c>
@@ -21779,8 +22249,9 @@
       <c r="N471">
         <v>202</v>
       </c>
-    </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O471" s="2"/>
+    </row>
+    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>518</v>
       </c>
@@ -21823,8 +22294,9 @@
       <c r="N472">
         <v>1165</v>
       </c>
-    </row>
-    <row r="473" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="O472" s="2"/>
+    </row>
+    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>519</v>
       </c>
@@ -21867,6 +22339,10 @@
       <c r="N473">
         <v>1659</v>
       </c>
+      <c r="O473" s="2"/>
+    </row>
+    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O474" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M473" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
